--- a/HW2/result/HW_2.xlsx
+++ b/HW2/result/HW_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\DADS7102\HW2\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75DCA443-00ED-49AE-B6F6-4BC3FED5573D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F586A1-1D82-47A4-874C-E19EAA72E8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{743BE6A8-4582-4DE1-BD9D-D3263963213D}"/>
   </bookViews>

--- a/HW2/result/HW_2.xlsx
+++ b/HW2/result/HW_2.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\DADS7102\HW2\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F586A1-1D82-47A4-874C-E19EAA72E8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B09636-449D-4F00-BC42-76C9D598A0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{743BE6A8-4582-4DE1-BD9D-D3263963213D}"/>
   </bookViews>
   <sheets>
-    <sheet name="HW_2" sheetId="1" r:id="rId1"/>
+    <sheet name="Farmer" sheetId="1" r:id="rId1"/>
+    <sheet name="Fractional" sheetId="2" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
     <definedName name="AFinish">[1]project!$K$6</definedName>
@@ -33,18 +34,18 @@
     <definedName name="LFinish">[1]project!$K$17</definedName>
     <definedName name="MFinish">[1]project!$K$18</definedName>
     <definedName name="NFinish">[1]project!$K$19</definedName>
-    <definedName name="solver_adj" localSheetId="0" hidden="1">HW_2!$C$3:$F$5</definedName>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">Farmer!$C$3:$F$5</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_lhs1" localSheetId="0" hidden="1">HW_2!$I$12:$I$13</definedName>
-    <definedName name="solver_lhs2" localSheetId="0" hidden="1">HW_2!$I$9:$I$11</definedName>
-    <definedName name="solver_lhs3" localSheetId="0" hidden="1">HW_2!$I$11</definedName>
-    <definedName name="solver_lhs4" localSheetId="0" hidden="1">HW_2!$I$11</definedName>
-    <definedName name="solver_lhs5" localSheetId="0" hidden="1">HW_2!$I$11</definedName>
-    <definedName name="solver_lhs6" localSheetId="0" hidden="1">HW_2!#REF!</definedName>
+    <definedName name="solver_lhs1" localSheetId="0" hidden="1">Farmer!$I$12:$I$13</definedName>
+    <definedName name="solver_lhs2" localSheetId="0" hidden="1">Farmer!$I$9:$I$11</definedName>
+    <definedName name="solver_lhs3" localSheetId="0" hidden="1">Farmer!$I$11</definedName>
+    <definedName name="solver_lhs4" localSheetId="0" hidden="1">Farmer!$I$11</definedName>
+    <definedName name="solver_lhs5" localSheetId="0" hidden="1">Farmer!$I$11</definedName>
+    <definedName name="solver_lhs6" localSheetId="0" hidden="1">Farmer!#REF!</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
@@ -53,7 +54,7 @@
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_opt" localSheetId="0" hidden="1">HW_2!$E$10</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">Farmer!$E$10</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">3</definedName>
@@ -62,12 +63,12 @@
     <definedName name="solver_rel4" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel5" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel6" localSheetId="0" hidden="1">3</definedName>
-    <definedName name="solver_rhs1" localSheetId="0" hidden="1">HW_2!$K$12:$K$13</definedName>
-    <definedName name="solver_rhs2" localSheetId="0" hidden="1">HW_2!$K$9:$K$11</definedName>
-    <definedName name="solver_rhs3" localSheetId="0" hidden="1">HW_2!$K$11</definedName>
-    <definedName name="solver_rhs4" localSheetId="0" hidden="1">HW_2!$K$11</definedName>
-    <definedName name="solver_rhs5" localSheetId="0" hidden="1">HW_2!$K$11</definedName>
-    <definedName name="solver_rhs6" localSheetId="0" hidden="1">HW_2!#REF!</definedName>
+    <definedName name="solver_rhs1" localSheetId="0" hidden="1">Farmer!$K$12:$K$13</definedName>
+    <definedName name="solver_rhs2" localSheetId="0" hidden="1">Farmer!$K$9:$K$11</definedName>
+    <definedName name="solver_rhs3" localSheetId="0" hidden="1">Farmer!$K$11</definedName>
+    <definedName name="solver_rhs4" localSheetId="0" hidden="1">Farmer!$K$11</definedName>
+    <definedName name="solver_rhs5" localSheetId="0" hidden="1">Farmer!$K$11</definedName>
+    <definedName name="solver_rhs6" localSheetId="0" hidden="1">Farmer!#REF!</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">2</definedName>
@@ -1009,4 +1010,13 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0181110-8A22-41AD-B4DC-22BED4234CBA}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>